--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,1129 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129598202</v>
+      </c>
+      <c r="B3" t="n">
+        <v>105793</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Myrarna, Myrarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>426257</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6609874</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129598590</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>426324</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6609797</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt på grov granlåga</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129598831</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>426314</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6609806</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På samma granlåga som rynkskinn</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129598363</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Myrarna, Myrarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>426257</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6609818</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129598374</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Myrarna, Myrarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>426232</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6609819</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars-Inge Hedlund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars-Inge Hedlund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129600785</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>426271</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6609661</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129598144</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Myrarna, Myrarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>426254</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6609869</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spridd över ca 50 kvm</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129603575</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gubbfallet, Gubbfallet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>425969</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6609583</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129599604</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Myrarna, Myrarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>426254</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6609869</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129600180</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>426318</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6609732</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1336,50 +1336,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129600785</v>
+        <v>129598144</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Myrarna, Myrarna, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426271</v>
+        <v>426254</v>
       </c>
       <c r="R8" t="n">
-        <v>6609661</v>
+        <v>6609869</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1430,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spridd över ca 50 kvm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,59 +1462,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129598144</v>
+        <v>129600785</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>5197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Myrarna, Myrarna, Vrm</t>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426254</v>
+        <v>426271</v>
       </c>
       <c r="R9" t="n">
-        <v>6609869</v>
+        <v>6609661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,12 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spridd över ca 50 kvm</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1908,6 +1908,863 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129624764</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91777</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skogen Ö om Björketorp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>426271</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6609722</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Carl A Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Carl A Andersson, Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129620521</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91777</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>426216</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6609711</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129624770</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skogen Ö om Björketorp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>426252</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6609824</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Carl A Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Carl A Andersson, Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129624765</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96073</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skogen Ö om Björketorp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>426297</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6609729</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Carl A Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Carl A Andersson, Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129619580</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92203</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>426235</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6609707</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129618249</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91777</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>426318</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6609802</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På grov granlåga med rynkskinn och ullticka</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129624761</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96989</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2583</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skogstrådmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fuscocephaloziopsis affinis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med hanorgan</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skogen Ö om Björketorp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>425984</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6609583</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Carl A Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Carl A Andersson, Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129624760</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90935</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skogen Ö om Björketorp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>425984</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6609583</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Carl A Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Carl A Andersson, Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -1336,59 +1336,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129598144</v>
+        <v>129600785</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Myrarna, Myrarna, Vrm</t>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426254</v>
+        <v>426271</v>
       </c>
       <c r="R8" t="n">
-        <v>6609869</v>
+        <v>6609661</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,12 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spridd över ca 50 kvm</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,50 +1448,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129600785</v>
+        <v>129598144</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Myrarna, Myrarna, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426271</v>
+        <v>426254</v>
       </c>
       <c r="R9" t="n">
-        <v>6609661</v>
+        <v>6609869</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1542,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spridd över ca 50 kvm</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1336,50 +1336,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129600785</v>
+        <v>129598144</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Myrarna, Myrarna, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426271</v>
+        <v>426254</v>
       </c>
       <c r="R8" t="n">
-        <v>6609661</v>
+        <v>6609869</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1430,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spridd över ca 50 kvm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,59 +1462,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129598144</v>
+        <v>129600785</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>5197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Myrarna, Myrarna, Vrm</t>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426254</v>
+        <v>426271</v>
       </c>
       <c r="R9" t="n">
-        <v>6609869</v>
+        <v>6609661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,12 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spridd över ca 50 kvm</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2016,10 +2016,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129620521</v>
+        <v>129624770</v>
       </c>
       <c r="B14" t="n">
-        <v>91777</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,34 +2027,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1106</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Skogen Ö om Björketorp, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>426216</v>
+        <v>426252</v>
       </c>
       <c r="R14" t="n">
-        <v>6609711</v>
+        <v>6609824</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,22 +2081,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,57 +2101,66 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson, Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624770</v>
+        <v>129619580</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>92203</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skogen Ö om Björketorp, Vrm</t>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426252</v>
+        <v>426235</v>
       </c>
       <c r="R15" t="n">
-        <v>6609824</v>
+        <v>6609707</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,12 +2187,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,12 +2222,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl A Andersson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl A Andersson, Olle Kvarnbäck</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2317,10 +2331,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129619580</v>
+        <v>129624760</v>
       </c>
       <c r="B17" t="n">
-        <v>92203</v>
+        <v>90935</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,43 +2342,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>5685</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Skogen Ö om Björketorp, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>426235</v>
+        <v>425984</v>
       </c>
       <c r="R17" t="n">
-        <v>6609707</v>
+        <v>6609583</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,27 +2396,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:54</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,22 +2416,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson, Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129618249</v>
+        <v>129624761</v>
       </c>
       <c r="B18" t="n">
-        <v>91777</v>
+        <v>96989</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2449,43 +2439,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1106</v>
+        <v>2583</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Skogstrådmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Fuscocephaloziopsis affinis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med hanorgan</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Skogen Ö om Björketorp, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>426318</v>
+        <v>425984</v>
       </c>
       <c r="R18" t="n">
-        <v>6609802</v>
+        <v>6609583</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,27 +2501,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På grov granlåga med rynkskinn och ullticka</t>
+          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2541,71 +2520,67 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson, Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624761</v>
+        <v>129603808</v>
       </c>
       <c r="B19" t="n">
-        <v>96989</v>
+        <v>92036</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2583</v>
+        <v>5467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogstrådmossa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscocephaloziopsis affinis</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med hanorgan</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skogen Ö om Björketorp, Vrm</t>
+          <t>Gubbfallet, Gubbfallet, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425984</v>
+        <v>425986</v>
       </c>
       <c r="R19" t="n">
-        <v>6609583</v>
+        <v>6609585</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2635,14 +2610,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2658,112 +2643,15 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Carl A Andersson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carl A Andersson, Olle Kvarnbäck</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>129624760</v>
-      </c>
-      <c r="B20" t="n">
-        <v>90935</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>5685</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Gullgröppa</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Pseudomerulius aureus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Skogen Ö om Björketorp, Vrm</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>425984</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6609583</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Karlstad</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Nyed</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Carl A Andersson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Carl A Andersson, Olle Kvarnbäck</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129598202</v>
       </c>
       <c r="B3" t="n">
-        <v>105793</v>
+        <v>105822</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,45 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129598590</v>
+        <v>129598831</v>
       </c>
       <c r="B4" t="n">
-        <v>92006</v>
+        <v>91581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>426324</v>
+        <v>426314</v>
       </c>
       <c r="R4" t="n">
-        <v>6609797</v>
+        <v>6609806</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt på grov granlåga</t>
+          <t>På samma granlåga som rynkskinn</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,50 +1011,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129598831</v>
+        <v>129598590</v>
       </c>
       <c r="B5" t="n">
-        <v>91553</v>
+        <v>92034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>426314</v>
+        <v>426324</v>
       </c>
       <c r="R5" t="n">
-        <v>6609806</v>
+        <v>6609797</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På samma granlåga som rynkskinn</t>
+          <t>Rikligt på grov granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1126,7 @@
         <v>129598363</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>129598374</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>129598144</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129603575</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>129624764</v>
       </c>
       <c r="B13" t="n">
-        <v>91777</v>
+        <v>91805</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>129624770</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>129619580</v>
       </c>
       <c r="B15" t="n">
-        <v>92203</v>
+        <v>92231</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129624765</v>
       </c>
       <c r="B16" t="n">
-        <v>96073</v>
+        <v>96102</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,35 +2331,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624760</v>
+        <v>129624761</v>
       </c>
       <c r="B17" t="n">
-        <v>90935</v>
+        <v>97018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5685</v>
+        <v>2583</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Skogstrådmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscocephaloziopsis affinis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med hanorgan</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2404,12 +2412,18 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2428,43 +2442,35 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624761</v>
+        <v>129624760</v>
       </c>
       <c r="B18" t="n">
-        <v>96989</v>
+        <v>90963</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2583</v>
+        <v>5685</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogstrådmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscocephaloziopsis affinis</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med hanorgan</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2509,18 +2515,12 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>129603808</v>
       </c>
       <c r="B19" t="n">
-        <v>92036</v>
+        <v>92064</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -2331,43 +2331,35 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624761</v>
+        <v>129624760</v>
       </c>
       <c r="B17" t="n">
-        <v>97018</v>
+        <v>90963</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2583</v>
+        <v>5685</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogstrådmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscocephaloziopsis affinis</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med hanorgan</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2412,18 +2404,12 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2442,35 +2428,43 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624760</v>
+        <v>129624761</v>
       </c>
       <c r="B18" t="n">
-        <v>90963</v>
+        <v>97018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5685</v>
+        <v>2583</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Skogstrådmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscocephaloziopsis affinis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med hanorgan</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2515,12 +2509,18 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129598202</v>
       </c>
       <c r="B3" t="n">
-        <v>105822</v>
+        <v>105834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,50 +894,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129598831</v>
+        <v>129598590</v>
       </c>
       <c r="B4" t="n">
-        <v>91581</v>
+        <v>92040</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>426314</v>
+        <v>426324</v>
       </c>
       <c r="R4" t="n">
-        <v>6609806</v>
+        <v>6609797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På samma granlåga som rynkskinn</t>
+          <t>Rikligt på grov granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,45 +1006,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129598590</v>
+        <v>129598831</v>
       </c>
       <c r="B5" t="n">
-        <v>92034</v>
+        <v>91587</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>426324</v>
+        <v>426314</v>
       </c>
       <c r="R5" t="n">
-        <v>6609797</v>
+        <v>6609806</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt på grov granlåga</t>
+          <t>På samma granlåga som rynkskinn</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1126,7 @@
         <v>129598363</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>129598374</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>129598144</v>
       </c>
       <c r="B8" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129603575</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>129624764</v>
       </c>
       <c r="B13" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>129624770</v>
       </c>
       <c r="B14" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129619580</v>
+        <v>129624765</v>
       </c>
       <c r="B15" t="n">
-        <v>92231</v>
+        <v>96114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,43 +2124,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Skogen Ö om Björketorp, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426235</v>
+        <v>426297</v>
       </c>
       <c r="R15" t="n">
-        <v>6609707</v>
+        <v>6609729</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,27 +2178,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:54</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2222,22 +2198,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson, Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624765</v>
+        <v>129619580</v>
       </c>
       <c r="B16" t="n">
-        <v>96102</v>
+        <v>92237</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,34 +2221,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skogen Ö om Björketorp, Vrm</t>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426297</v>
+        <v>426235</v>
       </c>
       <c r="R16" t="n">
-        <v>6609729</v>
+        <v>6609707</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2299,12 +2284,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,12 +2319,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl A Andersson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl A Andersson, Olle Kvarnbäck</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2334,7 +2334,7 @@
         <v>129624760</v>
       </c>
       <c r="B17" t="n">
-        <v>90963</v>
+        <v>90969</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>129624761</v>
       </c>
       <c r="B18" t="n">
-        <v>97018</v>
+        <v>97030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129603808</v>
       </c>
       <c r="B19" t="n">
-        <v>92064</v>
+        <v>92070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129598202</v>
       </c>
       <c r="B3" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129598590</v>
       </c>
       <c r="B4" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129598831</v>
       </c>
       <c r="B5" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>129598363</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>129598374</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,59 +1336,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129598144</v>
+        <v>129600785</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Myrarna, Myrarna, Vrm</t>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426254</v>
+        <v>426271</v>
       </c>
       <c r="R8" t="n">
-        <v>6609869</v>
+        <v>6609661</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,12 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spridd över ca 50 kvm</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,50 +1448,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129600785</v>
+        <v>129598144</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Myrarna, Myrarna, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426271</v>
+        <v>426254</v>
       </c>
       <c r="R9" t="n">
-        <v>6609661</v>
+        <v>6609869</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1542,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spridd över ca 50 kvm</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,7 +1577,7 @@
         <v>129603575</v>
       </c>
       <c r="B10" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>129624764</v>
       </c>
       <c r="B13" t="n">
-        <v>91811</v>
+        <v>91812</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>129624770</v>
       </c>
       <c r="B14" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624765</v>
+        <v>129619580</v>
       </c>
       <c r="B15" t="n">
-        <v>96114</v>
+        <v>92238</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,34 +2124,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2818</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skogen Ö om Björketorp, Vrm</t>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426297</v>
+        <v>426235</v>
       </c>
       <c r="R15" t="n">
-        <v>6609729</v>
+        <v>6609707</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,12 +2187,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,22 +2222,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl A Andersson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl A Andersson, Olle Kvarnbäck</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129619580</v>
+        <v>129624765</v>
       </c>
       <c r="B16" t="n">
-        <v>92237</v>
+        <v>96115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2221,43 +2245,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Skogen Ö om Björketorp, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426235</v>
+        <v>426297</v>
       </c>
       <c r="R16" t="n">
-        <v>6609707</v>
+        <v>6609729</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,27 +2299,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:54</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,47 +2319,55 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson, Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624760</v>
+        <v>129624761</v>
       </c>
       <c r="B17" t="n">
-        <v>90969</v>
+        <v>97031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5685</v>
+        <v>2583</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Skogstrådmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscocephaloziopsis affinis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med hanorgan</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2404,12 +2412,18 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2428,43 +2442,35 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624761</v>
+        <v>129624760</v>
       </c>
       <c r="B18" t="n">
-        <v>97030</v>
+        <v>90970</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2583</v>
+        <v>5685</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogstrådmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscocephaloziopsis affinis</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med hanorgan</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2509,18 +2515,12 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>129603808</v>
       </c>
       <c r="B19" t="n">
-        <v>92070</v>
+        <v>92071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129598202</v>
       </c>
       <c r="B3" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129598590</v>
       </c>
       <c r="B4" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129598831</v>
       </c>
       <c r="B5" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>129598363</v>
       </c>
       <c r="B6" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>129598374</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>129598144</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>129624764</v>
       </c>
       <c r="B13" t="n">
-        <v>91812</v>
+        <v>91817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>129624770</v>
       </c>
       <c r="B14" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>129619580</v>
       </c>
       <c r="B15" t="n">
-        <v>92238</v>
+        <v>92243</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129624765</v>
       </c>
       <c r="B16" t="n">
-        <v>96115</v>
+        <v>96120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,43 +2331,35 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624761</v>
+        <v>129624760</v>
       </c>
       <c r="B17" t="n">
-        <v>97031</v>
+        <v>90975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2583</v>
+        <v>5685</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogstrådmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscocephaloziopsis affinis</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med hanorgan</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2412,18 +2404,12 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2442,35 +2428,43 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624760</v>
+        <v>129624761</v>
       </c>
       <c r="B18" t="n">
-        <v>90970</v>
+        <v>97036</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5685</v>
+        <v>2583</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Skogstrådmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscocephaloziopsis affinis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med hanorgan</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2515,12 +2509,18 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>129603808</v>
       </c>
       <c r="B19" t="n">
-        <v>92071</v>
+        <v>92076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -1336,50 +1336,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129600785</v>
+        <v>129598144</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Myrarna, Myrarna, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426271</v>
+        <v>426254</v>
       </c>
       <c r="R8" t="n">
-        <v>6609661</v>
+        <v>6609869</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1430,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spridd över ca 50 kvm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,59 +1462,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129598144</v>
+        <v>129600785</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>5197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Myrarna, Myrarna, Vrm</t>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426254</v>
+        <v>426271</v>
       </c>
       <c r="R9" t="n">
-        <v>6609869</v>
+        <v>6609661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,12 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spridd över ca 50 kvm</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129619580</v>
+        <v>129624765</v>
       </c>
       <c r="B15" t="n">
-        <v>92243</v>
+        <v>96120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,43 +2124,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Skogen Ö om Björketorp, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426235</v>
+        <v>426297</v>
       </c>
       <c r="R15" t="n">
-        <v>6609707</v>
+        <v>6609729</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,27 +2178,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:54</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2222,22 +2198,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson, Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624765</v>
+        <v>129619580</v>
       </c>
       <c r="B16" t="n">
-        <v>96120</v>
+        <v>92243</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,34 +2221,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skogen Ö om Björketorp, Vrm</t>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426297</v>
+        <v>426235</v>
       </c>
       <c r="R16" t="n">
-        <v>6609729</v>
+        <v>6609707</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2299,12 +2284,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,47 +2319,55 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl A Andersson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl A Andersson, Olle Kvarnbäck</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624760</v>
+        <v>129624761</v>
       </c>
       <c r="B17" t="n">
-        <v>90975</v>
+        <v>97036</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5685</v>
+        <v>2583</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Skogstrådmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscocephaloziopsis affinis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med hanorgan</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2404,12 +2412,18 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2428,43 +2442,35 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624761</v>
+        <v>129624760</v>
       </c>
       <c r="B18" t="n">
-        <v>97036</v>
+        <v>90975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2583</v>
+        <v>5685</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogstrådmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscocephaloziopsis affinis</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med hanorgan</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2509,18 +2515,12 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -2331,43 +2331,35 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624761</v>
+        <v>129624760</v>
       </c>
       <c r="B17" t="n">
-        <v>97036</v>
+        <v>90975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2583</v>
+        <v>5685</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogstrådmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscocephaloziopsis affinis</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med hanorgan</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2412,18 +2404,12 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2442,35 +2428,43 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624760</v>
+        <v>129624761</v>
       </c>
       <c r="B18" t="n">
-        <v>90975</v>
+        <v>97036</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5685</v>
+        <v>2583</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Skogstrådmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscocephaloziopsis affinis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med hanorgan</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2515,12 +2509,18 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129598202</v>
       </c>
       <c r="B3" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129598590</v>
       </c>
       <c r="B4" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129598831</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>129598363</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>129598374</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>129598144</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>129624764</v>
       </c>
       <c r="B13" t="n">
-        <v>91817</v>
+        <v>91821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>129624770</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624765</v>
+        <v>129619580</v>
       </c>
       <c r="B15" t="n">
-        <v>96120</v>
+        <v>92247</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,34 +2124,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2818</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skogen Ö om Björketorp, Vrm</t>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426297</v>
+        <v>426235</v>
       </c>
       <c r="R15" t="n">
-        <v>6609729</v>
+        <v>6609707</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,12 +2187,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,22 +2222,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl A Andersson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl A Andersson, Olle Kvarnbäck</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129619580</v>
+        <v>129624765</v>
       </c>
       <c r="B16" t="n">
-        <v>92243</v>
+        <v>96124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2221,43 +2245,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Skogen Ö om Björketorp, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426235</v>
+        <v>426297</v>
       </c>
       <c r="R16" t="n">
-        <v>6609707</v>
+        <v>6609729</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,27 +2299,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:54</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,47 +2319,55 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson, Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624760</v>
+        <v>129624761</v>
       </c>
       <c r="B17" t="n">
-        <v>90975</v>
+        <v>97040</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5685</v>
+        <v>2583</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Skogstrådmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscocephaloziopsis affinis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med hanorgan</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2404,12 +2412,18 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2428,43 +2442,35 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624761</v>
+        <v>129624760</v>
       </c>
       <c r="B18" t="n">
-        <v>97036</v>
+        <v>90979</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2583</v>
+        <v>5685</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogstrådmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscocephaloziopsis affinis</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med hanorgan</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2509,18 +2515,12 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>129603808</v>
       </c>
       <c r="B19" t="n">
-        <v>92076</v>
+        <v>92080</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129598202</v>
       </c>
       <c r="B3" t="n">
-        <v>105844</v>
+        <v>105846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129598590</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129598831</v>
       </c>
       <c r="B5" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>129598363</v>
       </c>
       <c r="B6" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>129598374</v>
       </c>
       <c r="B7" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,59 +1336,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129598144</v>
+        <v>129600785</v>
       </c>
       <c r="B8" t="n">
-        <v>98778</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Myrarna, Myrarna, Vrm</t>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426254</v>
+        <v>426271</v>
       </c>
       <c r="R8" t="n">
-        <v>6609869</v>
+        <v>6609661</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,12 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spridd över ca 50 kvm</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,50 +1448,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129600785</v>
+        <v>129598144</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>98780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Myrarna, Myrarna, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426271</v>
+        <v>426254</v>
       </c>
       <c r="R9" t="n">
-        <v>6609661</v>
+        <v>6609869</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1542,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spridd över ca 50 kvm</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1913,7 +1913,7 @@
         <v>129624764</v>
       </c>
       <c r="B13" t="n">
-        <v>91821</v>
+        <v>91823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>129624770</v>
       </c>
       <c r="B14" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>129619580</v>
       </c>
       <c r="B15" t="n">
-        <v>92247</v>
+        <v>92249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129624765</v>
       </c>
       <c r="B16" t="n">
-        <v>96124</v>
+        <v>96126</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>129624761</v>
       </c>
       <c r="B17" t="n">
-        <v>97040</v>
+        <v>97042</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>129624760</v>
       </c>
       <c r="B18" t="n">
-        <v>90979</v>
+        <v>90981</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129603808</v>
       </c>
       <c r="B19" t="n">
-        <v>92080</v>
+        <v>92082</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -1336,50 +1336,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129600785</v>
+        <v>129598144</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>98780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Myrarna, Myrarna, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426271</v>
+        <v>426254</v>
       </c>
       <c r="R8" t="n">
-        <v>6609661</v>
+        <v>6609869</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1430,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spridd över ca 50 kvm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,59 +1462,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129598144</v>
+        <v>129600785</v>
       </c>
       <c r="B9" t="n">
-        <v>98780</v>
+        <v>5197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Myrarna, Myrarna, Vrm</t>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426254</v>
+        <v>426271</v>
       </c>
       <c r="R9" t="n">
-        <v>6609869</v>
+        <v>6609661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,12 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spridd över ca 50 kvm</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,7 +790,7 @@
         <v>129598202</v>
       </c>
       <c r="B3" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>129598363</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>129598374</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,59 +1336,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129598144</v>
+        <v>129600785</v>
       </c>
       <c r="B8" t="n">
-        <v>98780</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Myrarna, Myrarna, Vrm</t>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426254</v>
+        <v>426271</v>
       </c>
       <c r="R8" t="n">
-        <v>6609869</v>
+        <v>6609661</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,12 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spridd över ca 50 kvm</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,50 +1448,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129600785</v>
+        <v>129598144</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>98790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Myrarna, Myrarna, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426271</v>
+        <v>426254</v>
       </c>
       <c r="R9" t="n">
-        <v>6609661</v>
+        <v>6609869</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1542,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spridd över ca 50 kvm</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2019,7 +2019,7 @@
         <v>129624770</v>
       </c>
       <c r="B14" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129624765</v>
       </c>
       <c r="B16" t="n">
-        <v>96126</v>
+        <v>96136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,43 +2331,35 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624761</v>
+        <v>129624760</v>
       </c>
       <c r="B17" t="n">
-        <v>97042</v>
+        <v>90981</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2583</v>
+        <v>5685</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogstrådmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscocephaloziopsis affinis</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med hanorgan</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2412,18 +2404,12 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2442,35 +2428,43 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624760</v>
+        <v>129624761</v>
       </c>
       <c r="B18" t="n">
-        <v>90981</v>
+        <v>97052</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5685</v>
+        <v>2583</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Skogstrådmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscocephaloziopsis affinis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med hanorgan</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2515,12 +2509,18 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2653,6 +2653,131 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129922764</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Myrarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>426254</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6609870</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>S-Kar-0459</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Spridd över ca 50 kvm</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -2331,35 +2331,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624760</v>
+        <v>129624761</v>
       </c>
       <c r="B17" t="n">
-        <v>90981</v>
+        <v>97052</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5685</v>
+        <v>2583</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Skogstrådmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscocephaloziopsis affinis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med hanorgan</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2404,12 +2412,18 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2428,43 +2442,35 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624761</v>
+        <v>129624760</v>
       </c>
       <c r="B18" t="n">
-        <v>97052</v>
+        <v>90981</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2583</v>
+        <v>5685</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogstrådmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscocephaloziopsis affinis</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lindb. ex Steph.) Váňa &amp; L.Söderstr.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med hanorgan</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogen Ö om Björketorp, Vrm</t>
@@ -2509,18 +2515,12 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Tillsammans med mängder av långfliksmossa och gullgröppa</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -2658,7 +2658,7 @@
         <v>129922764</v>
       </c>
       <c r="B20" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129598202</v>
       </c>
       <c r="B3" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129598590</v>
       </c>
       <c r="B4" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129598831</v>
       </c>
       <c r="B5" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>129598363</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>129598374</v>
       </c>
       <c r="B7" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>129598144</v>
       </c>
       <c r="B9" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129603575</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>129624764</v>
       </c>
       <c r="B13" t="n">
-        <v>91823</v>
+        <v>91826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>129624770</v>
       </c>
       <c r="B14" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129619580</v>
+        <v>129624765</v>
       </c>
       <c r="B15" t="n">
-        <v>92249</v>
+        <v>96140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,43 +2124,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Skogen Ö om Björketorp, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426235</v>
+        <v>426297</v>
       </c>
       <c r="R15" t="n">
-        <v>6609707</v>
+        <v>6609729</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,27 +2178,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:54</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2222,22 +2198,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson, Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624765</v>
+        <v>129619580</v>
       </c>
       <c r="B16" t="n">
-        <v>96136</v>
+        <v>92252</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,34 +2221,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skogen Ö om Björketorp, Vrm</t>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426297</v>
+        <v>426235</v>
       </c>
       <c r="R16" t="n">
-        <v>6609729</v>
+        <v>6609707</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2299,12 +2284,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,12 +2319,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl A Andersson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl A Andersson, Olle Kvarnbäck</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2334,7 +2334,7 @@
         <v>129624761</v>
       </c>
       <c r="B17" t="n">
-        <v>97052</v>
+        <v>97056</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>129624760</v>
       </c>
       <c r="B18" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129603808</v>
       </c>
       <c r="B19" t="n">
-        <v>92082</v>
+        <v>92085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129598202</v>
       </c>
       <c r="B3" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129598590</v>
       </c>
       <c r="B4" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129598831</v>
       </c>
       <c r="B5" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>129598363</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>129598374</v>
       </c>
       <c r="B7" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,50 +1336,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129600785</v>
+        <v>129598144</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>98797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Myrarna, Myrarna, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426271</v>
+        <v>426254</v>
       </c>
       <c r="R8" t="n">
-        <v>6609661</v>
+        <v>6609869</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1430,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spridd över ca 50 kvm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,59 +1462,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129598144</v>
+        <v>129600785</v>
       </c>
       <c r="B9" t="n">
-        <v>98794</v>
+        <v>5197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Myrarna, Myrarna, Vrm</t>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426254</v>
+        <v>426271</v>
       </c>
       <c r="R9" t="n">
-        <v>6609869</v>
+        <v>6609661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,12 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spridd över ca 50 kvm</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,7 +1577,7 @@
         <v>129603575</v>
       </c>
       <c r="B10" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>129624764</v>
       </c>
       <c r="B13" t="n">
-        <v>91826</v>
+        <v>91829</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>129624770</v>
       </c>
       <c r="B14" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624765</v>
+        <v>129619580</v>
       </c>
       <c r="B15" t="n">
-        <v>96140</v>
+        <v>92255</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,34 +2124,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2818</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skogen Ö om Björketorp, Vrm</t>
+          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426297</v>
+        <v>426235</v>
       </c>
       <c r="R15" t="n">
-        <v>6609729</v>
+        <v>6609707</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,12 +2187,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,22 +2222,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl A Andersson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl A Andersson, Olle Kvarnbäck</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129619580</v>
+        <v>129624765</v>
       </c>
       <c r="B16" t="n">
-        <v>92252</v>
+        <v>96143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2221,43 +2245,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björndalsmossen, Björndalsmossen, Vrm</t>
+          <t>Skogen Ö om Björketorp, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426235</v>
+        <v>426297</v>
       </c>
       <c r="R16" t="n">
-        <v>6609707</v>
+        <v>6609729</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,27 +2299,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:54</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,12 +2319,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Carl A Andersson, Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2334,7 +2334,7 @@
         <v>129624761</v>
       </c>
       <c r="B17" t="n">
-        <v>97056</v>
+        <v>97059</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>129624760</v>
       </c>
       <c r="B18" t="n">
-        <v>90984</v>
+        <v>90987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129603808</v>
       </c>
       <c r="B19" t="n">
-        <v>92085</v>
+        <v>92088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>129922764</v>
       </c>
       <c r="B20" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21840-2021 artfynd.xlsx
+++ b/artfynd/A 21840-2021 artfynd.xlsx
@@ -2542,7 +2542,7 @@
         <v>129603808</v>
       </c>
       <c r="B19" t="n">
-        <v>92088</v>
+        <v>92089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>129922764</v>
       </c>
       <c r="B20" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
